--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="83">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Ente dichiarante</t>
@@ -313,7 +319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -603,19 +609,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -626,16 +632,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -649,16 +655,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -672,7 +678,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -681,7 +687,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -695,16 +701,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -718,7 +724,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -727,7 +733,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -741,7 +747,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -750,7 +756,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -764,7 +770,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -773,7 +779,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -787,7 +793,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -796,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -810,7 +816,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -819,7 +825,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -833,7 +839,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -842,7 +848,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -856,19 +862,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
@@ -879,16 +885,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -902,7 +908,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -911,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -925,7 +931,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -934,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -948,7 +954,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -957,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -971,7 +977,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -980,10 +986,10 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -994,19 +1000,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1017,7 +1023,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
@@ -1026,10 +1032,10 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -1040,19 +1046,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1063,7 +1069,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
@@ -1072,7 +1078,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1086,13 +1092,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -1104,6 +1110,29 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="85">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -319,7 +325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -378,63 +384,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -443,90 +449,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -535,21 +541,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -558,21 +564,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -581,21 +587,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -604,21 +610,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -627,44 +633,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -673,12 +679,12 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -687,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -696,21 +702,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -719,21 +725,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -742,21 +748,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -765,21 +771,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -788,21 +794,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -811,21 +817,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -834,21 +840,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -857,21 +863,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -880,44 +886,44 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -926,21 +932,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -949,21 +955,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -972,21 +978,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -995,113 +1001,113 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1110,21 +1116,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1133,7 +1139,30 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
